--- a/docs/triton-learning/cards/triton-lesson-02-fused-softmax-oral.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-02-fused-softmax-oral.xlsx
@@ -36,16 +36,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">用 60 秒解释：增加 stages 为什么不保证提速？</t>
+          <t xml:space="preserve">persistent softmax 的一个 program 会通过行循环处理多行，num_stages 控制该循环的流水设置。请用约 60 秒解释：为什么增加 num_stages 不保证提速，应怎样理解重叠收益、驻留资源与实验归因？</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：stages 只提供跨迭代重叠机会，效果取决于有没有迭代可重叠，以及延迟隐藏收益与资源代价的权衡。
-• [T#B#作用域]：它作用于同一 program 的循环，不是独立 worker；grid=M 时每 program 只有一行，没有下一行迭代。
-• [T#B#收益与代价]：更多独立迭代在途可能改善指令级并行与延迟隐藏；额外资源占用也可能减少并行驻留。
-• [T#B#证据]：若 stages 连同资源和默认 grid 一起变化，只能评价联动策略；要作单因素归因需另设控制变量。
-[T#B,!c47f17#边界]：不要把变慢自动归因于 occupancy 下降，也不要把更多 stages 当作更多行内数据并行。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：增加 stages 只是增加跨迭代重叠的机会。有没有足够迭代，以及重叠收益能否超过资源和流水成本，才决定实际是否更快。
+• [T#B#作用域]：流水属于同一个 program 的行循环，不是新增独立 worker。若启动的 program 数等于行数，每个 program 只有一次行迭代，就没有自己的下一行可重叠。
+• [T#B#潜在收益]：多次独立迭代在途时，一次迭代等待数据，另一次可能推进指令，从而增加指令级并行与延迟隐藏机会。
+• [T#B#潜在代价]：若每个 program 使用更多受限资源，每个 SM 能同时驻留的 program 可能减少；但不能仅由驻留下降断言单个 stage 变慢。
+• [T#B#实验结论]：如果 stages、资源占用和默认 grid 一起变化，结果评价的是整套策略。要缩小归因范围，需要共同显式 grid 等追加对照。
+[T#B,!c47f17#边界]：occupancy 下降仍可能与加速同时出现，反过来相同 occupancy 也不保证相同速度；应以匹配当前配置的测量来判断。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -62,16 +63,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">用 60 秒说明：怎样审查本课 wrapper 性能比较？</t>
+          <t xml:space="preserve">要审查一份 persistent softmax 与其他实现的性能比较，测量对象是完成准备后的 wrapper 调用。请用约 60 秒说明：怎样核对计时边界、资源指标和正确性证据，并限制性能结论？</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：先统一计时边界，再核对实际特化、资源指标与正确性证据，最后收紧性能归因。
-• [T#B#计时]：JIT、资源和 grid 初始化在外；计时内保留 wrapper 的每次分配与检查，所有 providers 用同一口径。
-• [T#B#资源]：资源探测对应实际 launch 的特化；区分每 SM 理论资源上限、实际 grid 和运行时 achieved occupancy。
-• [T#B#正确性]：独立功能测试覆盖被比较的 shape 与配置；计时不能替代 reference 对照。
-[T#B,!c47f17#边界]：stage 与默认 grid 联动时，结论限于该策略；要隔离流水深度影响需追加控制变量。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：先确认各实现测的是同一调用场景，再核对被执行的编译配置、资源指标和独立功能测试，最后判断数据允许作出多强的性能归因。
+• [T#B#计时边界]：每个用例的 JIT、资源探测和 grid 初始化放在计时外；计时内保留常规 wrapper 调用中的分配、检查与启动。不能把这个结果与 kernel-only 或未缓存准备成本混用。
+• [T#B#资源对应]：资源记录必须来自实际 launch 的同一特化。每个 SM 的理论驻留上限、全设备实际启动的 grid，以及运行时 achieved occupancy，要分别解释。
+• [T#B#正确性证据]：独立功能测试应覆盖被比较的输入形状和配置，并提供 reference 对照；速度快或能运行结束本身都不能证明结果正确。
+• [T#B#性能归因]：若不同 stages 使用不同默认 grid，观测只支持当前联动策略的比较；要研究流水深度本身，还应加入共同 grid 等控制变量。
+[T#B,!c47f17#边界]：报告需要让读者知道结论适用于哪个实现、配置和测量场景。单一速度差异不足以直接证明某一种底层机制。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">

--- a/docs/triton-learning/cards/triton-lesson-02-fused-softmax-oral.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-02-fused-softmax-oral.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -36,17 +36,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">persistent softmax 的一个 program 会通过行循环处理多行，num_stages 控制该循环的流水设置。请用约 60 秒解释：为什么增加 num_stages 不保证提速，应怎样理解重叠收益、驻留资源与实验归因？</t>
+          <t xml:space="preserve">向面试官解释：在 Triton 3.7.1 的 persistent softmax 中，一个 program 用 tl.range 行循环处理多行，num_stages 控制这个循环的流水深度。为什么增加 num_stages 不保证提速？请用约 60 秒从重叠收益、驻留资源和实验归因三方面说明。</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：增加 stages 只是增加跨迭代重叠的机会。有没有足够迭代，以及重叠收益能否超过资源和流水成本，才决定实际是否更快。
-• [T#B#作用域]：流水属于同一个 program 的行循环，不是新增独立 worker。若启动的 program 数等于行数，每个 program 只有一次行迭代，就没有自己的下一行可重叠。
-• [T#B#潜在收益]：多次独立迭代在途时，一次迭代等待数据，另一次可能推进指令，从而增加指令级并行与延迟隐藏机会。
-• [T#B#潜在代价]：若每个 program 使用更多受限资源，每个 SM 能同时驻留的 program 可能减少；但不能仅由驻留下降断言单个 stage 变慢。
-• [T#B#实验结论]：如果 stages、资源占用和默认 grid 一起变化，结果评价的是整套策略。要缩小归因范围，需要共同显式 grid 等追加对照。
-[T#B,!c47f17#边界]：occupancy 下降仍可能与加速同时出现，反过来相同 occupancy 也不保证相同速度；应以匹配当前配置的测量来判断。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：增加 stages 只是增加跨迭代重叠的机会；有没有足够的迭代、重叠收益能否超过资源和流水成本，才决定是否更快。
+• [T#B#作用域]：流水属于同一 program 的行循环，不是新增 worker；若启动的 program 数等于行数，每个 program 只有一行，就没有可重叠的下一行。
+• [T#B#潜在收益]：多个独立行迭代在途时，一个等待数据，另一个可能推进指令，增加指令级并行与延迟隐藏机会。
+• [T#B#潜在代价]：每个 program 占用更多受限资源时，每个 SM 能同时驻留的 program 可能减少；但不能仅由驻留下降断言单个 stage 变慢。
+• [T#B#实验归因]：若 stages、资源占用和默认 grid 一起变化，结果评价的是整套策略；要缩小归因，需要共同显式 grid 等对照。
+[T#B,!c47f17#边界]：occupancy 下降仍可能与加速同时出现，相同 occupancy 也不保证相同速度。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -60,33 +60,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">要审查一份 persistent softmax 与其他实现的性能比较，测量对象是完成准备后的 wrapper 调用。请用约 60 秒说明：怎样核对计时边界、资源指标和正确性证据，并限制性能结论？</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：先确认各实现测的是同一调用场景，再核对被执行的编译配置、资源指标和独立功能测试，最后判断数据允许作出多强的性能归因。
-• [T#B#计时边界]：每个用例的 JIT、资源探测和 grid 初始化放在计时外；计时内保留常规 wrapper 调用中的分配、检查与启动。不能把这个结果与 kernel-only 或未缓存准备成本混用。
-• [T#B#资源对应]：资源记录必须来自实际 launch 的同一特化。每个 SM 的理论驻留上限、全设备实际启动的 grid，以及运行时 achieved occupancy，要分别解释。
-• [T#B#正确性证据]：独立功能测试应覆盖被比较的输入形状和配置，并提供 reference 对照；速度快或能运行结束本身都不能证明结果正确。
-• [T#B#性能归因]：若不同 stages 使用不同默认 grid，观测只支持当前联动策略的比较；要研究流水深度本身，还应加入共同 grid 等控制变量。
-[T#B,!c47f17#边界]：报告需要让读者知道结论适用于哪个实现、配置和测量场景。单一速度差异不足以直接证明某一种底层机制。</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">统一 wrapper 计时边界；实际 launch 同特化；理论与运行时指标分开；独立正确性覆盖；联动策略归因边界</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fused Softmax 学习日志 · 2026-08-07 · C #039–044、#112–122、#137、#148–152；D #001–006</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>